--- a/reference/MPP_Seed_Layout_Proposal.xlsx
+++ b/reference/MPP_Seed_Layout_Proposal.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$C$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Items'!$A$1:$Q$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Items'!$A$1:$Q$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Eligibility'!$A$1:$F$397</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Routes'!$A$1:$F$377</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOMs'!$A$1:$H$155</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Packaging'!$A$1:$J$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched'!$A$1:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DataIssues'!$A$1:$E$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Packaging'!$A$1:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DataIssues'!$A$1:$E$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -539,7 +539,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>158 items</t>
+          <t>160 items</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -666,11 +666,11 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>See Unmatched tab - 12 are off-site</t>
+          <t>See Unmatched tab - 14 are off-site</t>
         </is>
       </c>
     </row>
@@ -681,11 +681,11 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>17 HIGH / 35 MED / 12 LOW</t>
+          <t>13 HIGH / 39 MED / 14 LOW</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q159"/>
+  <dimension ref="A1:Q161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8725,7 +8725,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>19320-6A0 -A510</t>
+          <t>19320-6A0 -A510-AEP</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>6AO/6A0</t>
+          <t>6AO</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -8792,12 +8792,12 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>19410-6A0 -A000</t>
+          <t>19320-6A0 -A510-ISP</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>6A0 Water Passage (AEP)</t>
+          <t>6A0 Thermo Case Auto (ISP)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -8829,7 +8829,7 @@
       <c r="I125" s="3" t="inlineStr"/>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr"/>
@@ -8859,12 +8859,12 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>19321-64S -A000</t>
+          <t>19410-6A0 -A000-AEP</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>64S Thermo Case</t>
+          <t>6A0 Water Passage (AEP)</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>64S</t>
+          <t>6A0</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -8896,7 +8896,7 @@
       <c r="I126" s="3" t="inlineStr"/>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr"/>
@@ -8926,12 +8926,12 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>12270-6MA -J000</t>
+          <t>19410-6A0 -A000-ISP</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>6MA Fuel Pump</t>
+          <t>6A0 Water Passage (ISP)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>6MA</t>
+          <t>6A0</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -8963,7 +8963,7 @@
       <c r="I127" s="3" t="inlineStr"/>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr"/>
@@ -8993,12 +8993,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>19321-66V -A000</t>
+          <t>19321-64S -A000</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>66V Thermo Case</t>
+          <t>64S Thermo Case</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>66V</t>
+          <t>64S</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -9060,12 +9060,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>12270-6MD -A000</t>
+          <t>12270-6MA -J000</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>6MD Fuel Pump</t>
+          <t>6MA Fuel Pump</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>6MD</t>
+          <t>6MA</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9127,12 +9127,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>14850-6MD -A000</t>
+          <t>19321-66V -A000</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>6MD Oil Jet</t>
+          <t>66V Thermo Case</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>6MD</t>
+          <t>66V</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9164,7 +9164,7 @@
       <c r="I130" s="3" t="inlineStr"/>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr"/>
@@ -9194,12 +9194,12 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>19410-6MD -A000</t>
+          <t>12270-6MD -A000</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>6MD Water Passage</t>
+          <t>6MD Fuel Pump</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -9231,7 +9231,7 @@
       <c r="I131" s="3" t="inlineStr"/>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr"/>
@@ -9261,12 +9261,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>12230-P8A -A000</t>
+          <t>14850-6MD -A000</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Cam Thrust Front</t>
+          <t>6MD Oil Jet</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>P8A</t>
+          <t>6MD</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -9298,7 +9298,7 @@
       <c r="I132" s="3" t="inlineStr"/>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr"/>
@@ -9328,12 +9328,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>19321-66V-A100</t>
+          <t>19410-6MD -A000</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>66V Thermo Case</t>
+          <t>6MD Water Passage</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>66V</t>
+          <t>6MD</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
       <c r="I133" s="3" t="inlineStr"/>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr"/>
@@ -9393,148 +9393,148 @@
       <c r="Q133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>12231-RPY -G000-M</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>RPY Cam Holder In #1 (machined)</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>SubAssembly</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Machined</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>RPY/5BA</t>
-        </is>
-      </c>
-      <c r="G134" s="4" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>12230-P8A -A000</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Cam Thrust Front</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>FinishedGood</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>FinishedGood</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Assembled</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>P8A</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="H134" s="4" t="inlineStr"/>
-      <c r="I134" s="4" t="inlineStr"/>
-      <c r="J134" s="4" t="inlineStr"/>
-      <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="4" t="inlineStr"/>
-      <c r="M134" s="4" t="inlineStr">
-        <is>
-          <t>Blue Ridge (synthesized)</t>
-        </is>
-      </c>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr"/>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr"/>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>Off-Site</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O134" s="4" t="inlineStr">
-        <is>
-          <t>MA2-RPY6B2, MA2-RPYCAM1, MA2-RPYCAM2</t>
-        </is>
-      </c>
-      <c r="P134" s="4" t="inlineStr">
-        <is>
-          <t>SYNTHESIZED</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="inlineStr">
-        <is>
-          <t>Machined identity minted by Machining OUT from 12231-RPY -G000.</t>
-        </is>
-      </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>OFF-SITE</t>
+        </is>
+      </c>
+      <c r="Q134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>12232-RPY -G000-M</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>RPY Cam Holder In #2 (machined)</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>SubAssembly</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Machined</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>RPY/5BA</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>19321-66V-A100</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>66V Thermo Case</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>FinishedGood</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>FinishedGood</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Assembled</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>66V</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="H135" s="4" t="inlineStr"/>
-      <c r="I135" s="4" t="inlineStr"/>
-      <c r="J135" s="4" t="inlineStr"/>
-      <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="4" t="inlineStr"/>
-      <c r="M135" s="4" t="inlineStr">
-        <is>
-          <t>Blue Ridge (synthesized)</t>
-        </is>
-      </c>
-      <c r="N135" s="4" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr"/>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>Off-Site</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O135" s="4" t="inlineStr">
-        <is>
-          <t>MA2-RPY6B2, MA2-RPYCAM1, MA2-RPYCAM2</t>
-        </is>
-      </c>
-      <c r="P135" s="4" t="inlineStr">
-        <is>
-          <t>SYNTHESIZED</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="inlineStr">
-        <is>
-          <t>Machined identity minted by Machining OUT from 12232-RPY -G000.</t>
-        </is>
-      </c>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>OFF-SITE</t>
+        </is>
+      </c>
+      <c r="Q135" s="3" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>12233-RPY -G000-M</t>
+          <t>12231-RPY -G000-M</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder In #3 (machined)</t>
+          <t>RPY Cam Holder In #1 (machined)</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -9589,19 +9589,19 @@
       </c>
       <c r="Q136" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12233-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12231-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>12234-RPY -G000-M</t>
+          <t>12232-RPY -G000-M</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder In #4 (machined)</t>
+          <t>RPY Cam Holder In #2 (machined)</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -9656,19 +9656,19 @@
       </c>
       <c r="Q137" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12234-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12232-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>12235-RPY -G000-M</t>
+          <t>12233-RPY -G000-M</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder In #5 (machined)</t>
+          <t>RPY Cam Holder In #3 (machined)</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -9723,19 +9723,19 @@
       </c>
       <c r="Q138" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12235-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12233-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>12241-RPY -G000-M</t>
+          <t>12234-RPY -G000-M</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder Ex #1 (machined)</t>
+          <t>RPY Cam Holder In #4 (machined)</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -9790,19 +9790,19 @@
       </c>
       <c r="Q139" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12241-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12234-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>12242-RPY -G000-M</t>
+          <t>12235-RPY -G000-M</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder Ex #2 (machined)</t>
+          <t>RPY Cam Holder In #5 (machined)</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -9857,19 +9857,19 @@
       </c>
       <c r="Q140" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12242-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12235-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>12243-RPY -G000-M</t>
+          <t>12241-RPY -G000-M</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder Ex #3 (machined)</t>
+          <t>RPY Cam Holder Ex #1 (machined)</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -9924,19 +9924,19 @@
       </c>
       <c r="Q141" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12243-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12241-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>12244-RPY -G000-M</t>
+          <t>12242-RPY -G000-M</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder Ex #4 (machined)</t>
+          <t>RPY Cam Holder Ex #2 (machined)</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -9991,19 +9991,19 @@
       </c>
       <c r="Q142" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12244-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12242-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>12245-RPY -G000-M</t>
+          <t>12243-RPY -G000-M</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder Ex #5 (machined)</t>
+          <t>RPY Cam Holder Ex #3 (machined)</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -10058,19 +10058,19 @@
       </c>
       <c r="Q143" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12245-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12243-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>12246-RPY -G000-M</t>
+          <t>12244-RPY -G000-M</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>RPY Cam Holder Ex #6 (machined)</t>
+          <t>RPY Cam Holder Ex #4 (machined)</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -10125,19 +10125,19 @@
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12246-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12244-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>12261-RPY -G000-M</t>
+          <t>12245-RPY -G000-M</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>RPY Rocker Shaft #1 (machined)</t>
+          <t>RPY Cam Holder Ex #5 (machined)</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -10192,19 +10192,19 @@
       </c>
       <c r="Q145" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12261-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12245-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>12262-RPY -G000-M</t>
+          <t>12246-RPY -G000-M</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>RPY Rocker Shaft #2 (machined)</t>
+          <t>RPY Cam Holder Ex #6 (machined)</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -10259,19 +10259,19 @@
       </c>
       <c r="Q146" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12262-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12246-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>12263-RPY -G000-M</t>
+          <t>12261-RPY -G000-M</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>RPY Rocker Shaft #3 (machined)</t>
+          <t>RPY Rocker Shaft #1 (machined)</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -10326,19 +10326,19 @@
       </c>
       <c r="Q147" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12263-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12261-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>12264-RPY -G000-M</t>
+          <t>12262-RPY -G000-M</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>RPY Rocker Shaft #4 (machined)</t>
+          <t>RPY Rocker Shaft #2 (machined)</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -10393,19 +10393,19 @@
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12264-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12262-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>12265-RPY -G000-M</t>
+          <t>12263-RPY -G000-M</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>RPY Rocker Shaft #5 (machined)</t>
+          <t>RPY Rocker Shaft #3 (machined)</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>RPY</t>
+          <t>RPY/5BA</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1, MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2, MA2-RPYCAM1, MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
@@ -10460,19 +10460,19 @@
       </c>
       <c r="Q149" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12265-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12263-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>12271-RPY -G000-M</t>
+          <t>12264-RPY -G000-M</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>RPY Lower Cam Holder #1 (machined)</t>
+          <t>RPY Rocker Shaft #4 (machined)</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -10527,19 +10527,19 @@
       </c>
       <c r="Q150" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12271-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12264-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>12272-RPY -G000-M</t>
+          <t>12265-RPY -G000-M</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>RPY Lower Cam Holder #2 (machined)</t>
+          <t>RPY Rocker Shaft #5 (machined)</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>RPY/5BA</t>
+          <t>RPY</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2, MA2-RPYCAM1, MA2-RPYCAM2</t>
+          <t>MA2-RPYCAM1, MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
@@ -10594,19 +10594,19 @@
       </c>
       <c r="Q151" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12272-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12265-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>12273-RPY -G000-M</t>
+          <t>12271-RPY -G000-M</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>RPY Lower Cam Holder #3 (machined)</t>
+          <t>RPY Lower Cam Holder #1 (machined)</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -10661,19 +10661,19 @@
       </c>
       <c r="Q152" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12273-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12271-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>12274-RPY -G000-M</t>
+          <t>12272-RPY -G000-M</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>RPY Lower Cam Holder #4 (machined)</t>
+          <t>RPY Lower Cam Holder #2 (machined)</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -10728,19 +10728,19 @@
       </c>
       <c r="Q153" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12274-RPY -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12272-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>12265-5BA -G000-M</t>
+          <t>12273-RPY -G000-M</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>5BA Rocker Shaft #5 (machined)</t>
+          <t>RPY Lower Cam Holder #3 (machined)</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>5BA</t>
+          <t>RPY/5BA</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1, MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2, MA2-RPYCAM1, MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
@@ -10795,19 +10795,19 @@
       </c>
       <c r="Q154" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12265-5BA -G000.</t>
+          <t>Machined identity minted by Machining OUT from 12273-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>12265-6B2 -A000-M</t>
+          <t>12274-RPY -G000-M</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>5BA Rocker Shaft #5 (machined)</t>
+          <t>RPY Lower Cam Holder #4 (machined)</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>5BA</t>
+          <t>RPY/5BA</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1, MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2, MA2-RPYCAM1, MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
@@ -10862,19 +10862,19 @@
       </c>
       <c r="Q155" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12265-6B2 -A000.</t>
+          <t>Machined identity minted by Machining OUT from 12274-RPY -G000.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>12270-6NAA-M</t>
+          <t>12265-5BA -G000-M</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>6NA Fuel Pump Raw (machined)</t>
+          <t>5BA Rocker Shaft #5 (machined)</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>6NA</t>
+          <t>5BA</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>MA1-FP6NA</t>
+          <t>MA2-RPYCAM1, MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -10929,19 +10929,19 @@
       </c>
       <c r="Q156" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12270-6NAA.</t>
+          <t>Machined identity minted by Machining OUT from 12265-5BA -G000.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>12270-6VJA-M</t>
+          <t>12265-6B2 -A000-M</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>6VJ Fuel Pump Raw (machined)</t>
+          <t>5BA Rocker Shaft #5 (machined)</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>6VJ</t>
+          <t>5BA</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>MA1-FP6NA</t>
+          <t>MA2-RPYCAM1, MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
@@ -10996,19 +10996,19 @@
       </c>
       <c r="Q157" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12270-6VJA.</t>
+          <t>Machined identity minted by Machining OUT from 12265-6B2 -A000.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>12270-5PAA-M</t>
+          <t>12270-6NAA-M</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>5PA Fuel Pump Raw (machined)</t>
+          <t>6NA Fuel Pump Raw (machined)</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>6NA</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>MA2-5PA</t>
+          <t>MA1-FP6NA</t>
         </is>
       </c>
       <c r="P158" s="4" t="inlineStr">
@@ -11063,19 +11063,19 @@
       </c>
       <c r="Q158" s="4" t="inlineStr">
         <is>
-          <t>Machined identity minted by Machining OUT from 12270-5PAA.</t>
+          <t>Machined identity minted by Machining OUT from 12270-6NAA.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>12270-6B2A-M</t>
+          <t>12270-6VJA-M</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>6B2 Fuel Pump Raw (machined)</t>
+          <t>6VJ Fuel Pump Raw (machined)</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>6B2</t>
+          <t>6VJ</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -11120,22 +11120,156 @@
       </c>
       <c r="O159" s="4" t="inlineStr">
         <is>
+          <t>MA1-FP6NA</t>
+        </is>
+      </c>
+      <c r="P159" s="4" t="inlineStr">
+        <is>
+          <t>SYNTHESIZED</t>
+        </is>
+      </c>
+      <c r="Q159" s="4" t="inlineStr">
+        <is>
+          <t>Machined identity minted by Machining OUT from 12270-6VJA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>12270-5PAA-M</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>5PA Fuel Pump Raw (machined)</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>SubAssembly</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>Machined</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>5PA</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr"/>
+      <c r="I160" s="4" t="inlineStr"/>
+      <c r="J160" s="4" t="inlineStr"/>
+      <c r="K160" s="4" t="inlineStr"/>
+      <c r="L160" s="4" t="inlineStr"/>
+      <c r="M160" s="4" t="inlineStr">
+        <is>
+          <t>Blue Ridge (synthesized)</t>
+        </is>
+      </c>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>MA2-5PA</t>
+        </is>
+      </c>
+      <c r="P160" s="4" t="inlineStr">
+        <is>
+          <t>SYNTHESIZED</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="inlineStr">
+        <is>
+          <t>Machined identity minted by Machining OUT from 12270-5PAA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>12270-6B2A-M</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>6B2 Fuel Pump Raw (machined)</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>SubAssembly</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Machined</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>6B2</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr"/>
+      <c r="K161" s="4" t="inlineStr"/>
+      <c r="L161" s="4" t="inlineStr"/>
+      <c r="M161" s="4" t="inlineStr">
+        <is>
+          <t>Blue Ridge (synthesized)</t>
+        </is>
+      </c>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O161" s="4" t="inlineStr">
+        <is>
           <t>MA2-RPY6B2</t>
         </is>
       </c>
-      <c r="P159" s="4" t="inlineStr">
+      <c r="P161" s="4" t="inlineStr">
         <is>
           <t>SYNTHESIZED</t>
         </is>
       </c>
-      <c r="Q159" s="4" t="inlineStr">
+      <c r="Q161" s="4" t="inlineStr">
         <is>
           <t>Machined identity minted by Machining OUT from 12270-6B2A.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q159"/>
+  <autoFilter ref="A1:Q161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39243,7 +39377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -40169,7 +40303,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>19320-6A0 -A510</t>
+          <t>19320-6A0 -A510-AEP</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -40207,22 +40341,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>19410-6A0 -A000</t>
+          <t>19320-6A0 -A510-ISP</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>6A0 Water Passage (AEP)</t>
+          <t>6A0 Thermo Case Auto (ISP)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
@@ -40245,22 +40379,22 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>19321-64S -A000</t>
+          <t>19410-6A0 -A000-AEP</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>64S Thermo Case</t>
+          <t>6A0 Water Passage (AEP)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -40283,22 +40417,22 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>12270-6MA -J000</t>
+          <t>19410-6A0 -A000-ISP</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>6MA Fuel Pump</t>
+          <t>6A0 Water Passage (ISP)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -40321,12 +40455,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>19321-66V -A000</t>
+          <t>19321-64S -A000</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>66V Thermo Case</t>
+          <t>64S Thermo Case</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -40359,12 +40493,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>12270-6MD -A000</t>
+          <t>12270-6MA -J000</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>6MD Fuel Pump</t>
+          <t>6MA Fuel Pump</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -40395,62 +40529,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>14850-6MD -A000</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>6MD Oil Jet</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>19321-66V -A000</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>66V Thermo Case</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>ByVision</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Camera</t>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>ByWeight</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Scale</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>19410-6MD -A000</t>
+          <t>12270-6MD -A000</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>6MD Water Passage</t>
+          <t>6MD Fuel Pump</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -40471,62 +40605,62 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>12230-P8A -A000</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Cam Thrust Front</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>14850-6MD -A000</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>6MD Oil Jet</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>ByWeight</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>Scale</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>ByVision</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Camera</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>19321-66V-A100</t>
+          <t>19410-6MD -A000</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>66V Thermo Case</t>
+          <t>6MD Water Passage</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
@@ -40546,8 +40680,84 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>12230-P8A -A000</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Cam Thrust Front</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>ByWeight</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>19321-66V-A100</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>66V Thermo Case</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>ByWeight</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J33"/>
+  <autoFilter ref="A1:J35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40558,7 +40768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -40700,7 +40910,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>19320-6A0 -A510</t>
+          <t>19320-6A0 -A510-AEP</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -40715,7 +40925,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>6AO/6A0</t>
+          <t>6AO</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -40732,12 +40942,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>19410-6A0 -A000</t>
+          <t>19320-6A0 -A510-ISP</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>6A0 Water Passage (AEP)</t>
+          <t>6A0 Thermo Case Auto (ISP)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -40764,12 +40974,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>19321-64S -A000</t>
+          <t>19410-6A0 -A000-AEP</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>64S Thermo Case</t>
+          <t>6A0 Water Passage (AEP)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -40779,7 +40989,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>64S</t>
+          <t>6A0</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -40796,12 +41006,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>12270-6MA -J000</t>
+          <t>19410-6A0 -A000-ISP</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>6MA Fuel Pump</t>
+          <t>6A0 Water Passage (ISP)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -40811,7 +41021,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6MA</t>
+          <t>6A0</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -40828,12 +41038,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>19321-66V -A000</t>
+          <t>19321-64S -A000</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>66V Thermo Case</t>
+          <t>64S Thermo Case</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -40843,7 +41053,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>66V</t>
+          <t>64S</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -40860,12 +41070,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>12270-6MD -A000</t>
+          <t>12270-6MA -J000</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>6MD Fuel Pump</t>
+          <t>6MA Fuel Pump</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -40875,7 +41085,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6MD</t>
+          <t>6MA</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -40892,12 +41102,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>14850-6MD -A000</t>
+          <t>19321-66V -A000</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>6MD Oil Jet</t>
+          <t>66V Thermo Case</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -40907,7 +41117,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6MD</t>
+          <t>66V</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -40924,12 +41134,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>19410-6MD -A000</t>
+          <t>12270-6MD -A000</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>6MD Water Passage</t>
+          <t>6MD Fuel Pump</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -40956,12 +41166,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>12230-P8A -A000</t>
+          <t>14850-6MD -A000</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Cam Thrust Front</t>
+          <t>6MD Oil Jet</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -40971,7 +41181,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>P8A</t>
+          <t>6MD</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -40988,37 +41198,101 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>19410-6MD -A000</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>6MD Water Passage</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>FinishedGood</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>6MD</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Off-Site</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>12230-P8A -A000</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Cam Thrust Front</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>FinishedGood</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>P8A</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Off-Site</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>19321-66V-A100</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>66V Thermo Case</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>FinishedGood</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>66V</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Off-Site</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41029,7 +41303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -41371,22 +41645,22 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>19320-6A0 -A510</t>
+          <t>1223A-6B2 -A000</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Second packaging row for the same part (16 trays x 6 parts, Scale).</t>
+          <t>MPP typed this "Component", but it is a BOM parent with 22 components - it is an assembled part, not a raw one.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>UQ_ContainerConfig_ActiveItemId permits one active config. Row dropped; MPP must split the part number or pick one rule.</t>
+          <t>Treated as assembled (no die-cast route, no machined identity). MPP should re-type it as FinishedGood.</t>
         </is>
       </c>
     </row>
@@ -41398,130 +41672,130 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>19410-6A0 -A000</t>
+          <t>19321-66V -A000 / 19321-66V-A100</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Second packaging row for the same part (12 trays x 15 parts, Scale).</t>
+          <t>Two part numbers with the identical description "66V Thermo Case".</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>UQ_ContainerConfig_ActiveItemId permits one active config. Row dropped; MPP must split the part number or pick one rule.</t>
+          <t>Loaded as two items. MPP to confirm both are live, or retire one.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Parts</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>1223A-6B2 -A000</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>MPP typed this "Component", but it is a BOM parent with 22 components - it is an assembled part, not a raw one.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Treated as assembled (no die-cast route, no machined identity). MPP should re-type it as FinishedGood.</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>11200-6FB-A000</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Component "6FB Oil Pan Raw" appears in no BOM, so its line was inferred from program 6FB, which covers 2 finished goods.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Eligible at all of them: MA2-6FBCHOP. MPP should supply the BOM.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Parts</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>19320-6A0 -A510</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>One part number used for two different parts: 6A0 Thermo Case Auto (AEP) (basket 5); 6A0 Thermo Case Auto (ISP) (basket 6).</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>UQ_Item_PartNumber allows one row. MPP must supply a distinct number for the second variant, or confirm they are the same part.</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>12270-6B2 -A000 -&gt; 92900-06012-0B</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>BOM note says "10x12 Dowel Pin" but the part is "6x12 Stud Bolt".</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Item description kept. MPP to confirm the correct component.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Parts</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>19321-66V -A000 / 19321-66V-A100</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Two part numbers with the identical description "66V Thermo Case".</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Loaded as two items. MPP to confirm both are live, or retire one.</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>90009-R70-A000</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Component "14mm Bolt Plug" appears in no BOM, so its line was inferred from program 6FB/5J6-1, which covers 3 finished goods.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Eligible at all of them: MA2-6FBCHOP, MA2-V6OP. MPP should supply the BOM.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Parts</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>19410-6A0 -A000</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>One part number used for two different parts: 6A0 Water Passage (AEP) (basket 60); 6A0 Water Passage (ISP) (basket 15).</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>UQ_Item_PartNumber allows one row. MPP must supply a distinct number for the second variant, or confirm they are the same part.</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>94301-08140</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Component "8x14 Dowel Pin" appears in no BOM, so its line was inferred from program 6FB/5J6-1, which covers 3 finished goods.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Eligible at all of them: MA2-6FBCHOP, MA2-V6OP. MPP should supply the BOM.</t>
         </is>
       </c>
     </row>
@@ -41533,22 +41807,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>11200-6FB-A000</t>
+          <t>66B-TC</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Component "6FB Oil Pan Raw" appears in no BOM, so its line was inferred from program 6FB, which covers 2 finished goods.</t>
+          <t>Configured production line "66B Thermal Case" has no part assigned to it.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Eligible at all of them: MA2-6FBCHOP. MPP should supply the BOM.</t>
+          <t>Either MPP omitted its parts, or the line is idle.</t>
         </is>
       </c>
     </row>
@@ -41560,22 +41834,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>12270-6B2 -A000 -&gt; 92900-06012-0B</t>
+          <t>AO-OP</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>BOM note says "10x12 Dowel Pin" but the part is "6x12 Stud Bolt".</t>
+          <t>Configured production line "Assembly Out Oil Passage" has no part assigned to it.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Item description kept. MPP to confirm the correct component.</t>
+          <t>Either MPP omitted its parts, or the line is idle.</t>
         </is>
       </c>
     </row>
@@ -41587,22 +41861,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>90009-R70-A000</t>
+          <t>MA1-COMPBR</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Component "14mm Bolt Plug" appears in no BOM, so its line was inferred from program 6FB/5J6-1, which covers 3 finished goods.</t>
+          <t>Configured production line "RPY Comp bracket" has no part assigned to it.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Eligible at all of them: MA2-6FBCHOP, MA2-V6OP. MPP should supply the BOM.</t>
+          <t>Either MPP omitted its parts, or the line is idle.</t>
         </is>
       </c>
     </row>
@@ -41614,22 +41888,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>94301-08140</t>
+          <t>MA2-COS</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Component "8x14 Dowel Pin" appears in no BOM, so its line was inferred from program 6FB/5J6-1, which covers 3 finished goods.</t>
+          <t>Configured production line "Case Oil Seal" has no part assigned to it.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Eligible at all of them: MA2-6FBCHOP, MA2-V6OP. MPP should supply the BOM.</t>
+          <t>Either MPP omitted its parts, or the line is idle.</t>
         </is>
       </c>
     </row>
@@ -41641,22 +41915,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>66B-TC</t>
+          <t>12230-P8A -A000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Configured production line "66B Thermal Case" has no part assigned to it.</t>
+          <t>Closure is "Scale" (ByWeight) but no Target Weight was given.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Either MPP omitted its parts, or the line is idle.</t>
+          <t>TargetWeight left NULL - the scale close cannot validate without it.</t>
         </is>
       </c>
     </row>
@@ -41668,22 +41942,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>AO-OP</t>
+          <t>1223A-59B -A0002</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Configured production line "Assembly Out Oil Passage" has no part assigned to it.</t>
+          <t>Blue Ridge dev-seed part number appears in the customer workbook.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Either MPP omitted its parts, or the line is idle.</t>
+          <t>Row dropped - not an MPP part.</t>
         </is>
       </c>
     </row>
@@ -41695,22 +41969,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>MA1-COMPBR</t>
+          <t>12270-6MA -J000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Configured production line "RPY Comp bracket" has no part assigned to it.</t>
+          <t>Closure is "Scale" (ByWeight) but no Target Weight was given.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Either MPP omitted its parts, or the line is idle.</t>
+          <t>TargetWeight left NULL - the scale close cannot validate without it.</t>
         </is>
       </c>
     </row>
@@ -41722,22 +41996,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>MA2-COS</t>
+          <t>12270-6MD -A000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Configured production line "Case Oil Seal" has no part assigned to it.</t>
+          <t>Closure is "Scale" (ByWeight) but no Target Weight was given.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Either MPP omitted its parts, or the line is idle.</t>
+          <t>TargetWeight left NULL - the scale close cannot validate without it.</t>
         </is>
       </c>
     </row>
@@ -41754,7 +42028,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>12230-P8A -A000</t>
+          <t>14650-5GO -A000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -41781,17 +42055,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1223A-59B -A0002</t>
+          <t>14660-5GO -A000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Blue Ridge dev-seed part number appears in the customer workbook.</t>
+          <t>Closure is "Scale" (ByWeight) but no Target Weight was given.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Row dropped - not an MPP part.</t>
+          <t>TargetWeight left NULL - the scale close cannot validate without it.</t>
         </is>
       </c>
     </row>
@@ -41808,7 +42082,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>12270-6MA -J000</t>
+          <t>17145-6MD -A000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -41835,7 +42109,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>12270-6MD -A000</t>
+          <t>19320-6A0 -A010</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -41862,7 +42136,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>14650-5GO -A000</t>
+          <t>19320-6A0 -A510-AEP</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -41889,7 +42163,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>14660-5GO -A000</t>
+          <t>19320-6A0 -A510-ISP</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -41916,7 +42190,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>17145-6MD -A000</t>
+          <t>19321-64S -A000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -41943,7 +42217,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>19320-6A0 -A010</t>
+          <t>19321-66V -A000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -41970,7 +42244,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>19320-6A0 -A510</t>
+          <t>19321-66V-A100</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -41997,7 +42271,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>19321-64S -A000</t>
+          <t>1932A-69F -A000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -42024,7 +42298,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>19321-66V -A000</t>
+          <t>19410-6A0 -A000-AEP</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -42051,7 +42325,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>19321-66V-A100</t>
+          <t>19410-6A0 -A000-ISP</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -42078,7 +42352,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1932A-69F -A000</t>
+          <t>19410-6MD -A000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -42105,7 +42379,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>19410-6A0 -A000</t>
+          <t>22533-RJ2 -0000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -42132,17 +42406,17 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>19410-6MD -A000</t>
+          <t>5G0-FG</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Closure is "Scale" (ByWeight) but no Target Weight was given.</t>
+          <t>Blue Ridge dev-seed part number appears in the customer workbook.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>TargetWeight left NULL - the scale close cannot validate without it.</t>
+          <t>Row dropped - not an MPP part.</t>
         </is>
       </c>
     </row>
@@ -42154,22 +42428,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>22533-RJ2 -0000</t>
+          <t>11221-64AA-A010</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Closure is "Scale" (ByWeight) but no Target Weight was given.</t>
+          <t>Cannot tell from the data whether "Baffle Plate A" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>TargetWeight left NULL - the scale close cannot validate without it.</t>
+          <t>Classified as Cast. This drives the die-cast route + DC1/TRIM eligibility, so MPP should confirm.</t>
         </is>
       </c>
     </row>
@@ -42181,22 +42455,22 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>5G0-FG</t>
+          <t>11222-64A-A001</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Blue Ridge dev-seed part number appears in the customer workbook.</t>
+          <t>Cannot tell from the data whether "Baffle Plate B" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Row dropped - not an MPP part.</t>
+          <t>Classified as Cast. This drives the die-cast route + DC1/TRIM eligibility, so MPP should confirm.</t>
         </is>
       </c>
     </row>
@@ -42213,12 +42487,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>11221-64AA-A010</t>
+          <t>146315GO A000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Cannot tell from the data whether "Baffle Plate A" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
+          <t>Cannot tell from the data whether "Front In Shaft" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -42240,12 +42514,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>11222-64A-A001</t>
+          <t>146325GO A000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Cannot tell from the data whether "Baffle Plate B" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
+          <t>Cannot tell from the data whether "Front Ex Shaft" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -42267,12 +42541,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>146315GO A000</t>
+          <t>146335GO A000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Cannot tell from the data whether "Front In Shaft" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
+          <t>Cannot tell from the data whether "Rear In Shaft" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -42294,12 +42568,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>146325GO A000</t>
+          <t>146345GO A000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Cannot tell from the data whether "Front Ex Shaft" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
+          <t>Cannot tell from the data whether "Rear Ex Shaft" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -42321,17 +42595,17 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>146335GO A000</t>
+          <t>19320-6A0 -A510</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Cannot tell from the data whether "Rear In Shaft" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
+          <t>One part number used for two different parts: 6A0 Thermo Case Auto (AEP) (basket 5); 6A0 Thermo Case Auto (ISP) (basket 6).</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Classified as Cast. This drives the die-cast route + DC1/TRIM eligibility, so MPP should confirm.</t>
+          <t>Split into 19320-6A0 -A510-AEP, 19320-6A0 -A510-ISP. The suffix is a Blue Ridge convention, NOT an MPP part number, and MUST be stripped before the value reaches AIM -- Parts.ufn_AimCustomerPartNumber currently only strips dashes, so it would emit e.g. "193206A0 A510AEP". MPP should still confirm whether a real distinct number exists.</t>
         </is>
       </c>
     </row>
@@ -42348,17 +42622,17 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>146345GO A000</t>
+          <t>19410-6A0 -A000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Cannot tell from the data whether "Rear Ex Shaft" is die cast at MPP or purchased (shafts / baffle plates are commonly bought-in steel).</t>
+          <t>One part number used for two different parts: 6A0 Water Passage (AEP) (basket 60); 6A0 Water Passage (ISP) (basket 15).</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Classified as Cast. This drives the die-cast route + DC1/TRIM eligibility, so MPP should confirm.</t>
+          <t>Split into 19410-6A0 -A000-AEP, 19410-6A0 -A000-ISP. The suffix is a Blue Ridge convention, NOT an MPP part number, and MUST be stripped before the value reaches AIM -- Parts.ufn_AimCustomerPartNumber currently only strips dashes, so it would emit e.g. "193206A0 A510AEP". MPP should still confirm whether a real distinct number exists.</t>
         </is>
       </c>
     </row>
@@ -42618,7 +42892,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>19320-6A0 -A510</t>
+          <t>19320-6A0 -A510-AEP</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -42645,7 +42919,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>19321-64S -A000</t>
+          <t>19320-6A0 -A510-ISP</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -42672,7 +42946,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>19321-66V -A000</t>
+          <t>19321-64S -A000</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -42699,7 +42973,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>19321-66V-A100</t>
+          <t>19321-66V -A000</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -42726,7 +43000,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>19410-6A0 -A000</t>
+          <t>19321-66V-A100</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -42753,7 +43027,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>19410-6MD -A000</t>
+          <t>19410-6A0 -A000-AEP</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -42780,22 +43054,76 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>19410-6A0 -A000-ISP</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Finished good has no BOM rows.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Off-site part - no BOM expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>19410-6MD -A000</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Finished good has no BOM rows.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Off-site part - no BOM expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
           <t>22533-RJ2 -0000</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Finished good has no BOM rows.</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Off-site part - no BOM expected.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E65"/>
+  <autoFilter ref="A1:E67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reference/MPP_Seed_Layout_Proposal.xlsx
+++ b/reference/MPP_Seed_Layout_Proposal.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Items'!$A$1:$Q$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Eligibility'!$A$1:$F$397</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Routes'!$A$1:$F$377</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOMs'!$A$1:$H$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOMs'!$A$1:$H$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Packaging'!$A$1:$J$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DataIssues'!$A$1:$E$67</definedName>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -39365,8 +39365,996 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>12231-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #1 (machined)</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>12231-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #1</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>12232-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #2 (machined)</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>12232-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #2</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>12233-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #3 (machined)</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>12233-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #3</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>12234-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #4 (machined)</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>12234-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #4</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>12235-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #5 (machined)</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>12235-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder In #5</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>12241-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #1 (machined)</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>12241-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #1</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>12242-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #2 (machined)</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>12242-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #2</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>12243-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #3 (machined)</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>12243-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #3</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>12244-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #4 (machined)</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>12244-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #4</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>12245-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #5 (machined)</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>12245-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #5</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>12246-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #6 (machined)</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>12246-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>RPY Cam Holder Ex #6</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>12261-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #1 (machined)</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>12261-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #1</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>12262-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #2 (machined)</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>12262-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #2</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>12263-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #3 (machined)</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>12263-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #3</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>12264-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #4 (machined)</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>12264-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #4</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>12265-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #5 (machined)</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>12265-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>RPY Rocker Shaft #5</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>12271-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>RPY Lower Cam Holder #1 (machined)</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>12271-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>RPY Lower Cam Holder #1</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>12272-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>RPY Lower Cam Holder #2 (machined)</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>12272-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>RPY Lower Cam Holder #2</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>12273-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>RPY Lower Cam Holder #3 (machined)</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>12273-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>RPY Lower Cam Holder #3</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>12274-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>RPY Lower Cam Holder #4 (machined)</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>12274-RPY -G000</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>RPY Lower Cam Holder #4</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>12265-5BA -G000-M</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>5BA Rocker Shaft #5 (machined)</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>12265-5BA -G000</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>5BA Rocker Shaft #5</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>12265-6B2 -A000-M</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>5BA Rocker Shaft #5 (machined)</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>12265-6B2 -A000</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>5BA Rocker Shaft #5</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>12270-6NAA-M</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>6NA Fuel Pump Raw (machined)</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>12270-6NAA</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>6NA Fuel Pump Raw</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>12270-6VJA-M</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>6VJ Fuel Pump Raw (machined)</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>12270-6VJA</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>6VJ Fuel Pump Raw</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>12270-5PAA-M</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>5PA Fuel Pump Raw (machined)</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>12270-5PAA</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>5PA Fuel Pump Raw</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>12270-6B2A-M</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>6B2 Fuel Pump Raw (machined)</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>12270-6B2A</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>6B2 Fuel Pump Raw</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>machining mint (derived)</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>Machining OUT consumes the casting to mint this identity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H155"/>
+  <autoFilter ref="A1:H181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reference/MPP_Seed_Layout_Proposal.xlsx
+++ b/reference/MPP_Seed_Layout_Proposal.xlsx
@@ -19,11 +19,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$C$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Items'!$A$1:$Q$161</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Eligibility'!$A$1:$F$397</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Eligibility'!$A$1:$F$411</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Routes'!$A$1:$F$377</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOMs'!$A$1:$H$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Packaging'!$A$1:$J$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DataIssues'!$A$1:$E$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-RJ2-PB</t>
         </is>
       </c>
       <c r="P122" s="3" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6A0-TCM</t>
         </is>
       </c>
       <c r="P123" s="3" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6A0-TCA-AEP</t>
         </is>
       </c>
       <c r="P124" s="3" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6A0-TCA-ISP</t>
         </is>
       </c>
       <c r="P125" s="3" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6A0-WP-AEP</t>
         </is>
       </c>
       <c r="P126" s="3" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6A0-WP-ISP</t>
         </is>
       </c>
       <c r="P127" s="3" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-64S-TC</t>
         </is>
       </c>
       <c r="P128" s="3" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6MA-FP</t>
         </is>
       </c>
       <c r="P129" s="3" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-66V-TC</t>
         </is>
       </c>
       <c r="P130" s="3" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6MD-FP</t>
         </is>
       </c>
       <c r="P131" s="3" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6MD-OJ</t>
         </is>
       </c>
       <c r="P132" s="3" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-6MD-WP</t>
         </is>
       </c>
       <c r="P133" s="3" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-P8A-CT</t>
         </is>
       </c>
       <c r="P134" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>OS-66V-TC-A100</t>
         </is>
       </c>
       <c r="P135" s="3" t="inlineStr">
@@ -11280,7 +11280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F397"/>
+  <dimension ref="A1:F411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21196,17 +21196,17 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>12231-RPY -G000-M</t>
+          <t>22533-RJ2 -0000</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>OS-RJ2-PB</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RVS Piston Brake</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -21219,24 +21219,24 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>12231-RPY -G000-M</t>
+          <t>19320-6A0 -A010</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>OS-6A0-TCM</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>6A0 Thermo Case Manual</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
@@ -21249,24 +21249,24 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>12231-RPY -G000-M</t>
+          <t>19320-6A0 -A510-AEP</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>OS-6A0-TCA-AEP</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>6A0 Thermo Case Auto (AEP)</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
@@ -21279,24 +21279,24 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>12232-RPY -G000-M</t>
+          <t>19320-6A0 -A510-ISP</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>OS-6A0-TCA-ISP</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>6A0 Thermo Case Auto (ISP)</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
@@ -21309,24 +21309,24 @@
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>12232-RPY -G000-M</t>
+          <t>19410-6A0 -A000-AEP</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>OS-6A0-WP-AEP</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>6A0 Water Passage (AEP)</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
@@ -21339,24 +21339,24 @@
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>12232-RPY -G000-M</t>
+          <t>19410-6A0 -A000-ISP</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>OS-6A0-WP-ISP</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>6A0 Water Passage (ISP)</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
@@ -21369,24 +21369,24 @@
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>12233-RPY -G000-M</t>
+          <t>19321-64S -A000</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>OS-64S-TC</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>64S Thermo Case</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
@@ -21399,24 +21399,24 @@
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>12233-RPY -G000-M</t>
+          <t>12270-6MA -J000</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>OS-6MA-FP</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>6MA Fuel Pump</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -21429,24 +21429,24 @@
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>12233-RPY -G000-M</t>
+          <t>19321-66V -A000</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>OS-66V-TC</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>66V Thermo Case</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
@@ -21459,24 +21459,24 @@
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>12234-RPY -G000-M</t>
+          <t>12270-6MD -A000</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>OS-6MD-FP</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>6MD Fuel Pump</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -21489,24 +21489,24 @@
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>12234-RPY -G000-M</t>
+          <t>14850-6MD -A000</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>OS-6MD-OJ</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>6MD Oil Jet</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
@@ -21519,24 +21519,24 @@
       </c>
       <c r="F341" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>12234-RPY -G000-M</t>
+          <t>19410-6MD -A000</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>OS-6MD-WP</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>6MD Water Passage</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
@@ -21549,24 +21549,24 @@
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>12235-RPY -G000-M</t>
+          <t>12230-P8A -A000</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>OS-P8A-CT</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>Cam Thrust Front</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
@@ -21579,24 +21579,24 @@
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>12235-RPY -G000-M</t>
+          <t>19321-66V-A100</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>OS-66V-TC-A100</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>66V Thermo Case (A100)</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -21609,24 +21609,24 @@
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>via BOM parent</t>
+          <t>off-site part; dedicated line under the Offsite facility</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>12235-RPY -G000-M</t>
+          <t>12231-RPY -G000-M</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
@@ -21646,17 +21646,17 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>12241-RPY -G000-M</t>
+          <t>12231-RPY -G000-M</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -21676,17 +21676,17 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>12241-RPY -G000-M</t>
+          <t>12231-RPY -G000-M</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
@@ -21706,17 +21706,17 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>12241-RPY -G000-M</t>
+          <t>12232-RPY -G000-M</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -21736,17 +21736,17 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>12242-RPY -G000-M</t>
+          <t>12232-RPY -G000-M</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -21766,17 +21766,17 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>12242-RPY -G000-M</t>
+          <t>12232-RPY -G000-M</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -21796,17 +21796,17 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>12242-RPY -G000-M</t>
+          <t>12233-RPY -G000-M</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -21826,17 +21826,17 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>12243-RPY -G000-M</t>
+          <t>12233-RPY -G000-M</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -21856,17 +21856,17 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>12243-RPY -G000-M</t>
+          <t>12233-RPY -G000-M</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -21886,17 +21886,17 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>12243-RPY -G000-M</t>
+          <t>12234-RPY -G000-M</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -21916,17 +21916,17 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>12244-RPY -G000-M</t>
+          <t>12234-RPY -G000-M</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -21946,17 +21946,17 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>12244-RPY -G000-M</t>
+          <t>12234-RPY -G000-M</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -21976,17 +21976,17 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>12244-RPY -G000-M</t>
+          <t>12235-RPY -G000-M</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
@@ -22006,17 +22006,17 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>12245-RPY -G000-M</t>
+          <t>12235-RPY -G000-M</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
@@ -22036,17 +22036,17 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>12245-RPY -G000-M</t>
+          <t>12235-RPY -G000-M</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
@@ -22066,17 +22066,17 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>12245-RPY -G000-M</t>
+          <t>12241-RPY -G000-M</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -22096,17 +22096,17 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>12246-RPY -G000-M</t>
+          <t>12241-RPY -G000-M</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -22126,17 +22126,17 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>12246-RPY -G000-M</t>
+          <t>12241-RPY -G000-M</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -22156,17 +22156,17 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>12246-RPY -G000-M</t>
+          <t>12242-RPY -G000-M</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -22186,17 +22186,17 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>12261-RPY -G000-M</t>
+          <t>12242-RPY -G000-M</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -22216,17 +22216,17 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>12261-RPY -G000-M</t>
+          <t>12242-RPY -G000-M</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
@@ -22246,17 +22246,17 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>12261-RPY -G000-M</t>
+          <t>12243-RPY -G000-M</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -22276,17 +22276,17 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>12262-RPY -G000-M</t>
+          <t>12243-RPY -G000-M</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -22306,17 +22306,17 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>12262-RPY -G000-M</t>
+          <t>12243-RPY -G000-M</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
@@ -22336,17 +22336,17 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>12262-RPY -G000-M</t>
+          <t>12244-RPY -G000-M</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
@@ -22366,17 +22366,17 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>12263-RPY -G000-M</t>
+          <t>12244-RPY -G000-M</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -22396,17 +22396,17 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>12263-RPY -G000-M</t>
+          <t>12244-RPY -G000-M</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -22426,17 +22426,17 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>12263-RPY -G000-M</t>
+          <t>12245-RPY -G000-M</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -22456,17 +22456,17 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>12264-RPY -G000-M</t>
+          <t>12245-RPY -G000-M</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
@@ -22486,17 +22486,17 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>12264-RPY -G000-M</t>
+          <t>12245-RPY -G000-M</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
@@ -22516,17 +22516,17 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>12264-RPY -G000-M</t>
+          <t>12246-RPY -G000-M</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -22546,7 +22546,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>12265-RPY -G000-M</t>
+          <t>12246-RPY -G000-M</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -22576,7 +22576,7 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>12265-RPY -G000-M</t>
+          <t>12246-RPY -G000-M</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -22606,7 +22606,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>12271-RPY -G000-M</t>
+          <t>12261-RPY -G000-M</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>12271-RPY -G000-M</t>
+          <t>12261-RPY -G000-M</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -22666,7 +22666,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>12271-RPY -G000-M</t>
+          <t>12261-RPY -G000-M</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -22696,7 +22696,7 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>12272-RPY -G000-M</t>
+          <t>12262-RPY -G000-M</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>12272-RPY -G000-M</t>
+          <t>12262-RPY -G000-M</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>12272-RPY -G000-M</t>
+          <t>12262-RPY -G000-M</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -22786,7 +22786,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>12273-RPY -G000-M</t>
+          <t>12263-RPY -G000-M</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -22816,7 +22816,7 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>12273-RPY -G000-M</t>
+          <t>12263-RPY -G000-M</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -22846,7 +22846,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>12273-RPY -G000-M</t>
+          <t>12263-RPY -G000-M</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>12274-RPY -G000-M</t>
+          <t>12264-RPY -G000-M</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -22906,7 +22906,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>12274-RPY -G000-M</t>
+          <t>12264-RPY -G000-M</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -22936,7 +22936,7 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>12274-RPY -G000-M</t>
+          <t>12264-RPY -G000-M</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -22966,7 +22966,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>12265-5BA -G000-M</t>
+          <t>12265-RPY -G000-M</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>12265-5BA -G000-M</t>
+          <t>12265-RPY -G000-M</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -23026,17 +23026,17 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>12265-6B2 -A000-M</t>
+          <t>12271-RPY -G000-M</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM1</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 1 Cam Holders</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -23056,17 +23056,17 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>12265-6B2 -A000-M</t>
+          <t>12271-RPY -G000-M</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPYCAM2</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>RPY Line 2 Cam holders</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
@@ -23086,17 +23086,17 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>12270-6NAA-M</t>
+          <t>12271-RPY -G000-M</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>MA1-FP6NA</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Fuel Pump (6NA 6VJ)</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -23116,17 +23116,17 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>12270-6VJA-M</t>
+          <t>12272-RPY -G000-M</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>MA1-FP6NA</t>
+          <t>MA2-RPY6B2</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>Fuel Pump (6NA 6VJ)</t>
+          <t>RPY 6b2 line2</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
@@ -23146,17 +23146,17 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>12270-5PAA-M</t>
+          <t>12272-RPY -G000-M</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>MA2-5PA</t>
+          <t>MA2-RPYCAM1</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>5PA Fuel Pump</t>
+          <t>RPY Line 1 Cam Holders</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -23176,17 +23176,17 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>12270-6B2A-M</t>
+          <t>12272-RPY -G000-M</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>MA2-RPY6B2</t>
+          <t>MA2-RPYCAM2</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>RPY 6b2 line2</t>
+          <t>RPY Line 2 Cam holders</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
@@ -23203,8 +23203,428 @@
         </is>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>12273-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPY6B2</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>RPY 6b2 line2</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>12273-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPYCAM1</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>RPY Line 1 Cam Holders</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>12273-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPYCAM2</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>RPY Line 2 Cam holders</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>12274-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPY6B2</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>RPY 6b2 line2</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>12274-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPYCAM1</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>RPY Line 1 Cam Holders</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>12274-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPYCAM2</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>RPY Line 2 Cam holders</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>12265-5BA -G000-M</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPYCAM1</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>RPY Line 1 Cam Holders</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>12265-5BA -G000-M</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPYCAM2</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>RPY Line 2 Cam holders</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>12265-6B2 -A000-M</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPYCAM1</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>RPY Line 1 Cam Holders</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>12265-6B2 -A000-M</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPYCAM2</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>RPY Line 2 Cam holders</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>12270-6NAA-M</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>MA1-FP6NA</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>Fuel Pump (6NA 6VJ)</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>12270-6VJA-M</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>MA1-FP6NA</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>Fuel Pump (6NA 6VJ)</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>12270-5PAA-M</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>MA2-5PA</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>5PA Fuel Pump</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>12270-6B2A-M</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>MA2-RPY6B2</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>RPY 6b2 line2</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>ProductionLine</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>via BOM parent</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F397"/>
+  <autoFilter ref="A1:F411"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41756,7 +42176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -41831,456 +42251,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>22533-RJ2 -0000</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>RVS Piston Brake</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>RJ2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>19320-6A0 -A010</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>6A0 Thermo Case Manual</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>6A0</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>19320-6A0 -A510-AEP</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>6A0 Thermo Case Auto (AEP)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>6AO</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>19320-6A0 -A510-ISP</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>6A0 Thermo Case Auto (ISP)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>6A0</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>19410-6A0 -A000-AEP</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>6A0 Water Passage (AEP)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>6A0</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>19410-6A0 -A000-ISP</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>6A0 Water Passage (ISP)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>6A0</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>19321-64S -A000</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>64S Thermo Case</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>64S</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>12270-6MA -J000</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>6MA Fuel Pump</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>6MA</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>19321-66V -A000</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>66V Thermo Case</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>66V</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>12270-6MD -A000</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>6MD Fuel Pump</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>6MD</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>14850-6MD -A000</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>6MD Oil Jet</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>6MD</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>19410-6MD -A000</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>6MD Water Passage</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>6MD</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>12230-P8A -A000</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Cam Thrust Front</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>P8A</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>19321-66V-A100</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>66V Thermo Case</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>FinishedGood</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>66V</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Off-Site</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Off-site part - manufactured away from Madison; no MPP line applies.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reference/MPP_Seed_Layout_Proposal.xlsx
+++ b/reference/MPP_Seed_Layout_Proposal.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$C$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Items'!$A$1:$Q$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Eligibility'!$A$1:$F$411</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Routes'!$A$1:$F$377</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Routes'!$A$1:$F$391</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOMs'!$A$1:$H$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Packaging'!$A$1:$J$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched'!$A$1:$F$2</definedName>
@@ -616,11 +616,11 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Across 112 routed items</t>
+          <t>Across 126 routed items</t>
         </is>
       </c>
     </row>
@@ -23635,7 +23635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F377"/>
+  <dimension ref="A1:F391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32885,12 +32885,12 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>12231-RPY -G000-M</t>
+          <t>22533-RJ2 -0000</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>12231-RPY -G000-M Route v1</t>
+          <t>22533-RJ2 -0000 Route v1</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
@@ -32898,12 +32898,12 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr"/>
@@ -32911,12 +32911,12 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>12232-RPY -G000-M</t>
+          <t>19320-6A0 -A010</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>12232-RPY -G000-M Route v1</t>
+          <t>19320-6A0 -A010 Route v1</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
@@ -32924,12 +32924,12 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr"/>
@@ -32937,12 +32937,12 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>12233-RPY -G000-M</t>
+          <t>19320-6A0 -A510-AEP</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>12233-RPY -G000-M Route v1</t>
+          <t>19320-6A0 -A510-AEP Route v1</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
@@ -32950,12 +32950,12 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr"/>
@@ -32963,12 +32963,12 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>12234-RPY -G000-M</t>
+          <t>19320-6A0 -A510-ISP</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>12234-RPY -G000-M Route v1</t>
+          <t>19320-6A0 -A510-ISP Route v1</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
@@ -32976,12 +32976,12 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr"/>
@@ -32989,12 +32989,12 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>12235-RPY -G000-M</t>
+          <t>19410-6A0 -A000-AEP</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>12235-RPY -G000-M Route v1</t>
+          <t>19410-6A0 -A000-AEP Route v1</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
@@ -33002,12 +33002,12 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr"/>
@@ -33015,12 +33015,12 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>12241-RPY -G000-M</t>
+          <t>19410-6A0 -A000-ISP</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>12241-RPY -G000-M Route v1</t>
+          <t>19410-6A0 -A000-ISP Route v1</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
@@ -33028,12 +33028,12 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr"/>
@@ -33041,12 +33041,12 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>12242-RPY -G000-M</t>
+          <t>19321-64S -A000</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>12242-RPY -G000-M Route v1</t>
+          <t>19321-64S -A000 Route v1</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
@@ -33054,12 +33054,12 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr"/>
@@ -33067,12 +33067,12 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>12243-RPY -G000-M</t>
+          <t>12270-6MA -J000</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>12243-RPY -G000-M Route v1</t>
+          <t>12270-6MA -J000 Route v1</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
@@ -33080,12 +33080,12 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr"/>
@@ -33093,12 +33093,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>12244-RPY -G000-M</t>
+          <t>19321-66V -A000</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>12244-RPY -G000-M Route v1</t>
+          <t>19321-66V -A000 Route v1</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
@@ -33106,12 +33106,12 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr"/>
@@ -33119,12 +33119,12 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>12245-RPY -G000-M</t>
+          <t>12270-6MD -A000</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>12245-RPY -G000-M Route v1</t>
+          <t>12270-6MD -A000 Route v1</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
@@ -33132,12 +33132,12 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr"/>
@@ -33145,12 +33145,12 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>12246-RPY -G000-M</t>
+          <t>14850-6MD -A000</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>12246-RPY -G000-M Route v1</t>
+          <t>14850-6MD -A000 Route v1</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
@@ -33158,12 +33158,12 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr"/>
@@ -33171,12 +33171,12 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>12261-RPY -G000-M</t>
+          <t>19410-6MD -A000</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>12261-RPY -G000-M Route v1</t>
+          <t>19410-6MD -A000 Route v1</t>
         </is>
       </c>
       <c r="C363" s="2" t="n">
@@ -33184,12 +33184,12 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr"/>
@@ -33197,12 +33197,12 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>12262-RPY -G000-M</t>
+          <t>12230-P8A -A000</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>12262-RPY -G000-M Route v1</t>
+          <t>12230-P8A -A000 Route v1</t>
         </is>
       </c>
       <c r="C364" s="2" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr"/>
@@ -33223,12 +33223,12 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>12263-RPY -G000-M</t>
+          <t>19321-66V-A100</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>12263-RPY -G000-M Route v1</t>
+          <t>19321-66V-A100 Route v1</t>
         </is>
       </c>
       <c r="C365" s="2" t="n">
@@ -33236,12 +33236,12 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>MachiningOut</t>
+          <t>AssemblyOut</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>Machining out</t>
+          <t>Assembly out</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr"/>
@@ -33249,12 +33249,12 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>12264-RPY -G000-M</t>
+          <t>12231-RPY -G000-M</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>12264-RPY -G000-M Route v1</t>
+          <t>12231-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C366" s="2" t="n">
@@ -33275,12 +33275,12 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>12265-RPY -G000-M</t>
+          <t>12232-RPY -G000-M</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>12265-RPY -G000-M Route v1</t>
+          <t>12232-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
@@ -33301,12 +33301,12 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>12271-RPY -G000-M</t>
+          <t>12233-RPY -G000-M</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>12271-RPY -G000-M Route v1</t>
+          <t>12233-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
@@ -33327,12 +33327,12 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>12272-RPY -G000-M</t>
+          <t>12234-RPY -G000-M</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>12272-RPY -G000-M Route v1</t>
+          <t>12234-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
@@ -33353,12 +33353,12 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>12273-RPY -G000-M</t>
+          <t>12235-RPY -G000-M</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>12273-RPY -G000-M Route v1</t>
+          <t>12235-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
@@ -33379,12 +33379,12 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>12274-RPY -G000-M</t>
+          <t>12241-RPY -G000-M</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>12274-RPY -G000-M Route v1</t>
+          <t>12241-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
@@ -33405,12 +33405,12 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>12265-5BA -G000-M</t>
+          <t>12242-RPY -G000-M</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>12265-5BA -G000-M Route v1</t>
+          <t>12242-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
@@ -33431,12 +33431,12 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>12265-6B2 -A000-M</t>
+          <t>12243-RPY -G000-M</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>12265-6B2 -A000-M Route v1</t>
+          <t>12243-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C373" s="2" t="n">
@@ -33457,12 +33457,12 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>12270-6NAA-M</t>
+          <t>12244-RPY -G000-M</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>12270-6NAA-M Route v1</t>
+          <t>12244-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
@@ -33483,12 +33483,12 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>12270-6VJA-M</t>
+          <t>12245-RPY -G000-M</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>12270-6VJA-M Route v1</t>
+          <t>12245-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
@@ -33509,12 +33509,12 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>12270-5PAA-M</t>
+          <t>12246-RPY -G000-M</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>12270-5PAA-M Route v1</t>
+          <t>12246-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
@@ -33535,12 +33535,12 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>12270-6B2A-M</t>
+          <t>12261-RPY -G000-M</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>12270-6B2A-M Route v1</t>
+          <t>12261-RPY -G000-M Route v1</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
@@ -33558,8 +33558,372 @@
       </c>
       <c r="F377" s="2" t="inlineStr"/>
     </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>12262-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>12262-RPY -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>12263-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>12263-RPY -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>12264-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>12264-RPY -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>12265-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>12265-RPY -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>12271-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>12271-RPY -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>12272-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>12272-RPY -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>12273-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>12273-RPY -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>12274-RPY -G000-M</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>12274-RPY -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>12265-5BA -G000-M</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>12265-5BA -G000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>12265-6B2 -A000-M</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>12265-6B2 -A000-M Route v1</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>12270-6NAA-M</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>12270-6NAA-M Route v1</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>12270-6VJA-M</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>12270-6VJA-M Route v1</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>12270-5PAA-M</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>12270-5PAA-M Route v1</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>12270-6B2A-M</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>12270-6B2A-M Route v1</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>MachiningOut</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Machining out</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F377"/>
+  <autoFilter ref="A1:F391"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
